--- a/jira_export_2026-08-06.xlsx
+++ b/jira_export_2026-08-06.xlsx
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2461,7 +2461,7 @@
         <v>2</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>367.5</v>
       </c>
       <c r="P97" s="18" t="n">
-        <v>10.5</v>
+        <v>10.36</v>
       </c>
     </row>
   </sheetData>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>25.75</v>
+        <v>26.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>8.5</v>
@@ -8265,7 +8265,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>8</v>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -8505,7 +8505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 2 commande(s)</t>
+          <t>Épics créées ce mois — 4 commande(s)</t>
         </is>
       </c>
     </row>
@@ -8605,94 +8605,142 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34979</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34975</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>00178226</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34970</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>00146508</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I6" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>2 commande(s)</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>dont Littéralis</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n"/>
-      <c r="G8" s="17" t="n"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>1 commande(s)</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B9" s="17" t="n"/>
@@ -8703,10 +8751,52 @@
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="inlineStr">
         <is>
+          <t>4 commande(s)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>dont Littéralis</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>3 commande(s)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="inlineStr">
+        <is>
           <t>1 commande(s)</t>
         </is>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="I11" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8721,13 +8811,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -8742,7 +8832,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2 clôture(s) : 2 projet(s), 0 rework</t>
+          <t>3 clôture(s) : 3 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -8839,32 +8929,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34848</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="17" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n">
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-08-06.xlsx
+++ b/jira_export_2026-08-06.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>71 h</t>
+          <t>86 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1669,7 @@
         <v>2</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>2</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
@@ -3350,32 +3350,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3385,34 +3385,34 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3422,12 +3422,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3462,27 +3462,27 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3494,27 +3494,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3545,16 +3545,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1079</v>
+        <v>1207</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3566,32 +3566,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3601,12 +3601,12 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3617,16 +3617,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>500</v>
+        <v>1079</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3638,32 +3638,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -3689,16 +3689,16 @@
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3710,32 +3710,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3761,16 +3761,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>1294.224</v>
+        <v>400</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3782,12 +3782,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3822,27 +3822,27 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>142.1</v>
+        <v>1294.224</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3854,32 +3854,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3889,32 +3889,32 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3926,27 +3926,27 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
@@ -3977,16 +3977,16 @@
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3998,32 +3998,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4033,32 +4033,32 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4070,28 +4070,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C47" s="11" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4101,32 +4105,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4138,27 +4142,23 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>Maxime PONTONNIER</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr"/>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4189,16 +4189,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>590.15</v>
+        <v>255</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4210,12 +4210,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4261,16 +4261,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4282,32 +4282,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4317,34 +4317,34 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O50" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="15" t="n">
@@ -4354,32 +4354,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4389,34 +4389,34 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
@@ -4426,32 +4426,32 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4477,16 +4477,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4498,12 +4498,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4549,16 +4549,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4570,32 +4570,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -4621,16 +4621,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4642,27 +4642,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4677,32 +4677,32 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4714,12 +4714,12 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
@@ -4765,16 +4765,16 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4786,32 +4786,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4821,32 +4821,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4858,12 +4858,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
@@ -4905,14 +4905,22 @@
         <v>6</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L58" s="14" t="inlineStr"/>
-      <c r="M58" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L58" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M58" s="14" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O58" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4922,27 +4930,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4952,7 +4960,7 @@
       </c>
       <c r="G59" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -4962,29 +4970,21 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M59" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L59" s="11" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr"/>
       <c r="N59" s="12" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
@@ -4994,32 +4994,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
@@ -5045,16 +5045,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5066,12 +5066,12 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5117,16 +5117,16 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5138,12 +5138,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5189,16 +5189,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5210,12 +5210,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5261,16 +5261,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5282,12 +5282,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5322,27 +5322,27 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K64" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5354,32 +5354,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5405,16 +5405,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5426,27 +5426,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5466,27 +5466,27 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5549,16 +5549,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5570,32 +5570,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5605,32 +5605,32 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K68" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5642,32 +5642,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5677,34 +5677,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>725</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
@@ -5981,18 +5981,18 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -6002,12 +6002,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6017,11 +6017,13 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E74" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -6040,29 +6042,29 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O74" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6072,12 +6074,12 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
@@ -6087,7 +6089,7 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -6110,29 +6112,29 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O75" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6142,28 +6144,26 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="n">
+        <v/>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -6182,29 +6182,29 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6214,27 +6214,27 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
@@ -6244,27 +6244,35 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L77" s="11" t="inlineStr"/>
-      <c r="M77" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
@@ -6278,26 +6286,28 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -6306,35 +6316,27 @@
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M78" s="14" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
       <c r="N78" s="15" t="n">
         <v>0</v>
       </c>
@@ -6397,12 +6399,12 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
@@ -6418,22 +6420,22 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E80" s="14" t="n">
@@ -6456,23 +6458,23 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
@@ -6533,16 +6535,16 @@
         <v>13</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
@@ -6573,7 +6575,7 @@
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E82" s="14" t="n">
@@ -6603,16 +6605,16 @@
         <v>13</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
@@ -6643,7 +6645,7 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
@@ -6673,16 +6675,16 @@
         <v>13</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
@@ -6698,22 +6700,22 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E84" s="14" t="n">
@@ -6731,34 +6733,34 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O84" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
@@ -6768,22 +6770,22 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
@@ -6799,24 +6801,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H85" s="11" t="inlineStr"/>
+      <c r="H85" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L85" s="11" t="inlineStr"/>
-      <c r="M85" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O85" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6826,22 +6840,22 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E86" s="14" t="n">
@@ -6857,11 +6871,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H86" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H86" s="14" t="inlineStr"/>
       <c r="I86" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -6871,18 +6881,10 @@
         <v>16</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L86" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M86" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L86" s="14" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
       <c r="N86" s="15" t="n">
         <v>0</v>
       </c>
@@ -6896,12 +6898,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6911,7 +6913,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6929,34 +6931,34 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6966,22 +6968,22 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E88" s="14" t="n">
@@ -6994,27 +6996,39 @@
       </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H88" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H88" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L88" s="14" t="inlineStr"/>
-      <c r="M88" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L88" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M88" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7024,22 +7038,22 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -7055,21 +7069,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H89" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H89" s="11" t="inlineStr"/>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L89" s="11" t="inlineStr"/>
       <c r="M89" s="11" t="inlineStr"/>
@@ -7086,22 +7096,22 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E90" s="14" t="n">
@@ -7109,44 +7119,36 @@
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M90" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
       <c r="N90" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7156,22 +7158,22 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -7179,7 +7181,7 @@
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7189,12 +7191,12 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
@@ -7205,16 +7207,16 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O91" s="16" t="n">
         <v>0</v>
@@ -7226,22 +7228,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7254,7 +7256,7 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -7264,21 +7266,29 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L92" s="14" t="inlineStr"/>
-      <c r="M92" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L92" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M92" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7288,22 +7298,22 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -7326,25 +7336,17 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K93" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="L93" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M93" s="11" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr"/>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
@@ -7358,12 +7360,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7373,7 +7375,7 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7386,7 +7388,7 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H94" s="14" t="inlineStr">
@@ -7396,23 +7398,23 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7428,22 +7430,22 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7456,17 +7458,17 @@
       </c>
       <c r="G95" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
@@ -7477,12 +7479,12 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7498,28 +7500,26 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="n">
+        <v/>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -7533,58 +7533,190 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M96" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
+      <c r="N96" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K97" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L96" s="14" t="inlineStr"/>
-      <c r="M96" s="14" t="inlineStr"/>
-      <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="17" t="inlineStr">
+      <c r="L97" s="11" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr"/>
+      <c r="N97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="inlineStr"/>
+      <c r="D98" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F98" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G98" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H98" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I98" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K98" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+      <c r="N98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr"/>
-      <c r="C97" s="17" t="inlineStr"/>
-      <c r="D97" s="17" t="inlineStr"/>
-      <c r="E97" s="17" t="inlineStr"/>
-      <c r="F97" s="17" t="inlineStr"/>
-      <c r="G97" s="17" t="inlineStr"/>
-      <c r="H97" s="17" t="inlineStr"/>
-      <c r="I97" s="17" t="inlineStr"/>
-      <c r="J97" s="17" t="inlineStr"/>
-      <c r="K97" s="17" t="inlineStr"/>
-      <c r="L97" s="17" t="inlineStr"/>
-      <c r="M97" s="17" t="inlineStr"/>
-      <c r="N97" s="18" t="n">
+      <c r="B99" s="17" t="inlineStr"/>
+      <c r="C99" s="17" t="inlineStr"/>
+      <c r="D99" s="17" t="inlineStr"/>
+      <c r="E99" s="17" t="inlineStr"/>
+      <c r="F99" s="17" t="inlineStr"/>
+      <c r="G99" s="17" t="inlineStr"/>
+      <c r="H99" s="17" t="inlineStr"/>
+      <c r="I99" s="17" t="inlineStr"/>
+      <c r="J99" s="17" t="inlineStr"/>
+      <c r="K99" s="17" t="inlineStr"/>
+      <c r="L99" s="17" t="inlineStr"/>
+      <c r="M99" s="17" t="inlineStr"/>
+      <c r="N99" s="18" t="n">
         <v>64154.894</v>
       </c>
-      <c r="O97" s="18" t="n">
+      <c r="O99" s="18" t="n">
         <v>367.5</v>
       </c>
-      <c r="P97" s="18" t="n">
-        <v>10.36</v>
+      <c r="P99" s="18" t="n">
+        <v>7.74</v>
       </c>
     </row>
   </sheetData>
@@ -7682,6 +7814,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8256,16 +8390,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>26.25</v>
+        <v>37.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>35.5</v>
+        <v>47.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>8</v>
@@ -8275,7 +8409,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -8317,7 +8451,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>27.75</v>
+        <v>30.75</v>
       </c>
     </row>
   </sheetData>
@@ -8402,10 +8536,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>378688</v>
+        <v>387238</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>136593</v>
+        <v>145143</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>242094</v>
@@ -8427,10 +8561,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>168704</v>
+        <v>173204</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>64979</v>
+        <v>69479</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103725</v>
@@ -8452,10 +8586,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>209984</v>
+        <v>214034</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>71615</v>
+        <v>75665</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>138370</v>
@@ -8599,7 +8733,7 @@
         </is>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="6">
@@ -8644,7 +8778,7 @@
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="7">
@@ -8734,7 +8868,7 @@
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>0</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
@@ -8755,7 +8889,7 @@
         </is>
       </c>
       <c r="I9" s="24" t="n">
-        <v>0</v>
+        <v>8550</v>
       </c>
     </row>
     <row r="10">
@@ -8776,7 +8910,7 @@
         </is>
       </c>
       <c r="I10" s="24" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="11">
@@ -8797,7 +8931,7 @@
         </is>
       </c>
       <c r="I11" s="24" t="n">
-        <v>0</v>
+        <v>4050</v>
       </c>
     </row>
   </sheetData>
